--- a/变电站/2026年7月/2026年7月应收租金.xlsx
+++ b/变电站/2026年7月/2026年7月应收租金.xlsx
@@ -760,13 +760,13 @@
       </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>2110</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>6</v>
@@ -786,11 +786,7 @@
       <c r="O5" s="2" t="n">
         <v>2012</v>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>水0用量按保底1吨;</t>
-        </is>
-      </c>
+      <c r="P5" s="2" t="n"/>
       <c r="Q5" s="2" t="b">
         <v>0</v>
       </c>
@@ -1116,25 +1112,21 @@
         <v>18</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>5701</v>
+        <v>5598</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>5701</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>电0度;</t>
-        </is>
-      </c>
+        <v>801</v>
+      </c>
+      <c r="P11" s="2" t="n"/>
       <c r="Q11" s="2" t="b">
         <v>0</v>
       </c>
@@ -2140,25 +2132,21 @@
         <v>18</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>8467</v>
+        <v>8334</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>8467</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>868</v>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>电0度;</t>
-        </is>
-      </c>
+        <v>1001</v>
+      </c>
+      <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="b">
         <v>0</v>
       </c>
@@ -2639,16 +2627,16 @@
       <c r="L38" s="3" t="n"/>
       <c r="M38" s="3" t="n"/>
       <c r="N38" s="3" t="n">
-        <v>3723</v>
+        <v>3959</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>29685</v>
+        <v>29921</v>
       </c>
       <c r="P38" s="3" t="n"/>
       <c r="Q38" s="3" t="n"/>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>共 36 户；总水费¥472 / 总电费¥3723 / 总房租¥24840 / 总应收¥29685</t>
+          <t>共 36 户；总水费¥472 / 总电费¥3959 / 总房租¥24840 / 总应收¥29921</t>
         </is>
       </c>
     </row>

--- a/变电站/2026年7月/2026年7月应收租金.xlsx
+++ b/变电站/2026年7月/2026年7月应收租金.xlsx
@@ -887,22 +887,18 @@
         <v>3398</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>3398</v>
+        <v>3400</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>626</v>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>电0度;</t>
-        </is>
-      </c>
+        <v>628</v>
+      </c>
+      <c r="P7" s="2" t="n"/>
       <c r="Q7" s="2" t="b">
         <v>0</v>
       </c>
@@ -1683,16 +1679,16 @@
         <v>4548</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>4619</v>
+        <v>4691</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>1047</v>
+        <v>1119</v>
       </c>
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="b">
@@ -2627,16 +2623,16 @@
       <c r="L38" s="3" t="n"/>
       <c r="M38" s="3" t="n"/>
       <c r="N38" s="3" t="n">
-        <v>3959</v>
+        <v>3961</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>29921</v>
+        <v>29923</v>
       </c>
       <c r="P38" s="3" t="n"/>
       <c r="Q38" s="3" t="n"/>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>共 36 户；总水费¥472 / 总电费¥3959 / 总房租¥24840 / 总应收¥29921</t>
+          <t>共 36 户；总水费¥472 / 总电费¥3961 / 总房租¥24840 / 总应收¥29923</t>
         </is>
       </c>
     </row>
